--- a/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Bridge_v12.xlsx
@@ -474,13 +474,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>47.48</v>
+        <v>47.52</v>
       </c>
       <c r="C2">
-        <v>43.02</v>
+        <v>41.08</v>
       </c>
       <c r="D2">
-        <v>4.928176795580107</v>
+        <v>7.268623024830701</v>
       </c>
       <c r="E2">
         <v>2.919999999999996</v>
@@ -489,31 +489,31 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>50.93213701657459</v>
+        <v>52.06818961625282</v>
       </c>
       <c r="H2">
-        <v>46.14786298342541</v>
+        <v>45.01181038374718</v>
       </c>
       <c r="I2">
-        <v>50.93213701657459</v>
+        <v>52.06818961625282</v>
       </c>
       <c r="J2">
-        <v>46.14786298342541</v>
+        <v>45.01181038374718</v>
       </c>
       <c r="K2">
-        <v>50.93213701657459</v>
+        <v>52.06818961625282</v>
       </c>
       <c r="L2">
-        <v>46.14786298342541</v>
+        <v>45.01181038374718</v>
       </c>
       <c r="M2">
         <v>2.92</v>
       </c>
       <c r="N2">
-        <v>4.784274033149172</v>
+        <v>7.05637923250565</v>
       </c>
       <c r="O2">
-        <v>4.928176795580112</v>
+        <v>7.268623024830707</v>
       </c>
     </row>
   </sheetData>
